--- a/btst_live_calls.xlsx
+++ b/btst_live_calls.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +630,166 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35:02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>158.04</v>
+      </c>
+      <c r="D7" t="n">
+        <v>159.63</v>
+      </c>
+      <c r="E7" t="n">
+        <v>157.05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>160</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Green Session Close, Above VWAP, Bullish DI, Trend Active, Resistance Breakout, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35:02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1329</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1335.43</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1324.98</v>
+      </c>
+      <c r="F8" t="n">
+        <v>145</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Above VWAP, Bullish DI, Trend Active, Resistance Breakout, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35:02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1008.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1014.05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1005.03</v>
+      </c>
+      <c r="F9" t="n">
+        <v>145</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Green Session Close, Above VWAP, Bullish DI, Trend Active, Inflowing CMF, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35:02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1174.47</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1159.08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>145</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Green Session Close, Above VWAP, Bullish DI, Trend Active, Inflowing CMF, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:35:02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1775</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1787.84</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1766.97</v>
+      </c>
+      <c r="F11" t="n">
+        <v>145</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Green Session Close, Above VWAP, Bullish DI, Trend Active, Inflowing CMF, Volume Surge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/btst_live_calls.xlsx
+++ b/btst_live_calls.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,166 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:41:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>158.04</v>
+      </c>
+      <c r="D12" t="n">
+        <v>159.63</v>
+      </c>
+      <c r="E12" t="n">
+        <v>157.05</v>
+      </c>
+      <c r="F12" t="n">
+        <v>160</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Green Session Close, Above VWAP, Bullish DI, Trend Active, Resistance Breakout, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:41:07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1174.47</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1159.08</v>
+      </c>
+      <c r="F13" t="n">
+        <v>145</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Green Session Close, Above VWAP, Bullish DI, Trend Active, Inflowing CMF, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:41:07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1775</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1787.84</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1766.97</v>
+      </c>
+      <c r="F14" t="n">
+        <v>145</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Green Session Close, Above VWAP, Bullish DI, Trend Active, Inflowing CMF, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:41:07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="D15" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="E15" t="n">
+        <v>354.13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>130</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Above VWAP, Bullish DI, Trend Active, Inflowing CMF, Volume Surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-04 11:41:07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1060.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1066.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1056.53</v>
+      </c>
+      <c r="F16" t="n">
+        <v>130</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Bullish Local Baseline, Above VWAP, Bullish DI, Trend Active, Inflowing CMF, Volume Surge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
